--- a/results/mindlin_uniaxial_ssss_table_9_1.xlsx
+++ b/results/mindlin_uniaxial_ssss_table_9_1.xlsx
@@ -506,10 +506,10 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>9559.14002011713</v>
+        <v>9449.325251489056</v>
       </c>
       <c r="E2" t="n">
-        <v>352.5497908445633</v>
+        <v>348.49972215323794</v>
       </c>
       <c r="F2" t="n">
         <v>27.040000000000003</v>
@@ -518,10 +518,10 @@
         <v>27.0</v>
       </c>
       <c r="H2" t="n">
-        <v>12.038083980937989</v>
+        <v>11.888303334069448</v>
       </c>
       <c r="I2" t="n">
-        <v>955914.0020117129</v>
+        <v>944932.5251489056</v>
       </c>
       <c r="J2" t="n">
         <v>73317.06126523524</v>
@@ -544,10 +544,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>2509.315742875655</v>
+        <v>2505.2745604849683</v>
       </c>
       <c r="E3" t="n">
-        <v>92.54585019698689</v>
+        <v>92.39680770952431</v>
       </c>
       <c r="F3" t="n">
         <v>13.20111111111111</v>
@@ -556,10 +556,10 @@
         <v>13.2</v>
       </c>
       <c r="H3" t="n">
-        <v>6.01045915135832</v>
+        <v>5.999169004172367</v>
       </c>
       <c r="I3" t="n">
-        <v>250931.57428756548</v>
+        <v>250527.45604849682</v>
       </c>
       <c r="J3" t="n">
         <v>35793.885802607656</v>
@@ -582,10 +582,10 @@
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>1870.8864334846255</v>
+        <v>1869.036965154195</v>
       </c>
       <c r="E4" t="n">
-        <v>68.99999575598368</v>
+        <v>68.93178567937693</v>
       </c>
       <c r="F4" t="n">
         <v>8.41</v>
@@ -594,10 +594,10 @@
         <v>8.41</v>
       </c>
       <c r="H4" t="n">
-        <v>7.204517925800675</v>
+        <v>7.196407334051954</v>
       </c>
       <c r="I4" t="n">
-        <v>187088.64334846256</v>
+        <v>186903.6965154195</v>
       </c>
       <c r="J4" t="n">
         <v>22803.124454165252</v>
@@ -620,10 +620,10 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>1564.5460584379625</v>
+        <v>1563.3435058769646</v>
       </c>
       <c r="E5" t="n">
-        <v>57.70188369541542</v>
+        <v>57.65753246162585</v>
       </c>
       <c r="F5" t="n">
         <v>6.25</v>
@@ -632,10 +632,10 @@
         <v>6.25</v>
       </c>
       <c r="H5" t="n">
-        <v>8.232301391266468</v>
+        <v>8.225205193860136</v>
       </c>
       <c r="I5" t="n">
-        <v>156454.60584379625</v>
+        <v>156334.35058769645</v>
       </c>
       <c r="J5" t="n">
         <v>16946.43612824409</v>
@@ -658,10 +658,10 @@
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>1433.711298724086</v>
+        <v>1432.9379589723042</v>
       </c>
       <c r="E6" t="n">
-        <v>52.876578586874835</v>
+        <v>52.848057112435846</v>
       </c>
       <c r="F6" t="n">
         <v>5.137777777777777</v>
@@ -670,10 +670,10 @@
         <v>5.14</v>
       </c>
       <c r="H6" t="n">
-        <v>9.291721610767162</v>
+        <v>9.286170285724971</v>
       </c>
       <c r="I6" t="n">
-        <v>143371.12987240858</v>
+        <v>143293.79589723042</v>
       </c>
       <c r="J6" t="n">
         <v>13930.723672355674</v>
@@ -696,10 +696,10 @@
         <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>1345.3653840617978</v>
+        <v>1344.6012112638493</v>
       </c>
       <c r="E7" t="n">
-        <v>49.618300784623365</v>
+        <v>49.59011739579143</v>
       </c>
       <c r="F7" t="n">
         <v>4.530816326530612</v>
@@ -708,10 +708,10 @@
         <v>4.53</v>
       </c>
       <c r="H7" t="n">
-        <v>9.951293808596663</v>
+        <v>9.94507343089852</v>
       </c>
       <c r="I7" t="n">
-        <v>134536.53840617978</v>
+        <v>134460.12112638494</v>
       </c>
       <c r="J7" t="n">
         <v>12284.990317817048</v>
@@ -734,10 +734,10 @@
         <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>1169.5319166389336</v>
+        <v>1168.9713573179058</v>
       </c>
       <c r="E8" t="n">
-        <v>43.133402348890904</v>
+        <v>43.11272841054829</v>
       </c>
       <c r="F8" t="n">
         <v>4.2025</v>
@@ -746,10 +746,10 @@
         <v>4.2</v>
       </c>
       <c r="H8" t="n">
-        <v>9.263748328112055</v>
+        <v>9.258828890076929</v>
       </c>
       <c r="I8" t="n">
-        <v>116953.19166389336</v>
+        <v>116897.13573179058</v>
       </c>
       <c r="J8" t="n">
         <v>11394.783652631326</v>
@@ -772,10 +772,10 @@
         <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>1180.5120559557847</v>
+        <v>1180.272241557562</v>
       </c>
       <c r="E9" t="n">
-        <v>43.53835988811028</v>
+        <v>43.52951531466988</v>
       </c>
       <c r="F9" t="n">
         <v>4.044567901234568</v>
@@ -784,10 +784,10 @@
         <v>4.04</v>
       </c>
       <c r="H9" t="n">
-        <v>9.764650501928918</v>
+        <v>9.762463723598977</v>
       </c>
       <c r="I9" t="n">
-        <v>118051.20559557847</v>
+        <v>118027.2241557562</v>
       </c>
       <c r="J9" t="n">
         <v>10966.561856738857</v>
@@ -810,10 +810,10 @@
         <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>1183.908990129914</v>
+        <v>1183.5090574494257</v>
       </c>
       <c r="E10" t="n">
-        <v>43.663641914535425</v>
+        <v>43.64889203300201</v>
       </c>
       <c r="F10" t="n">
         <v>4.0</v>
@@ -822,10 +822,10 @@
         <v>4.0</v>
       </c>
       <c r="H10" t="n">
-        <v>9.915910478633856</v>
+        <v>9.912223008250502</v>
       </c>
       <c r="I10" t="n">
-        <v>118390.89901299139</v>
+        <v>118350.90574494256</v>
       </c>
       <c r="J10" t="n">
         <v>10845.71912207622</v>
@@ -848,10 +848,10 @@
         <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>1208.5900650830777</v>
+        <v>1208.0682281265051</v>
       </c>
       <c r="E11" t="n">
-        <v>44.57390243946183</v>
+        <v>44.55465661719043</v>
       </c>
       <c r="F11" t="n">
         <v>4.036446280991736</v>
@@ -860,10 +860,10 @@
         <v>4.04</v>
       </c>
       <c r="H11" t="n">
-        <v>10.04285783496423</v>
+        <v>10.038089823468072</v>
       </c>
       <c r="I11" t="n">
-        <v>120859.00650830776</v>
+        <v>120806.82281265051</v>
       </c>
       <c r="J11" t="n">
         <v>10944.540653746379</v>
@@ -886,10 +886,10 @@
         <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>1223.2555744750505</v>
+        <v>1222.3959550351979</v>
       </c>
       <c r="E12" t="n">
-        <v>45.11477978385559</v>
+        <v>45.083076235933056</v>
       </c>
       <c r="F12" t="n">
         <v>4.134444444444444</v>
@@ -898,10 +898,10 @@
         <v>4.13</v>
       </c>
       <c r="H12" t="n">
-        <v>9.911932761480793</v>
+        <v>9.904264609604878</v>
       </c>
       <c r="I12" t="n">
-        <v>122325.55744750505</v>
+        <v>122239.59550351978</v>
       </c>
       <c r="J12" t="n">
         <v>11210.255792568223</v>
@@ -924,10 +924,10 @@
         <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>1170.426775783301</v>
+        <v>1169.9353929198705</v>
       </c>
       <c r="E13" t="n">
-        <v>43.166405569213886</v>
+        <v>43.14828292163654</v>
       </c>
       <c r="F13" t="n">
         <v>4.28171597633136</v>
@@ -936,10 +936,10 @@
         <v>4.28</v>
       </c>
       <c r="H13" t="n">
-        <v>9.081566784866363</v>
+        <v>9.077334218372572</v>
       </c>
       <c r="I13" t="n">
-        <v>117042.67757833011</v>
+        <v>116993.53929198705</v>
       </c>
       <c r="J13" t="n">
         <v>11609.572209949069</v>
@@ -962,10 +962,10 @@
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>1149.0153094068953</v>
+        <v>1148.5481296311684</v>
       </c>
       <c r="E14" t="n">
-        <v>42.37673118670758</v>
+        <v>42.359501171050034</v>
       </c>
       <c r="F14" t="n">
         <v>4.470204081632653</v>
@@ -974,10 +974,10 @@
         <v>4.47</v>
       </c>
       <c r="H14" t="n">
-        <v>8.479820252687507</v>
+        <v>8.475965839031463</v>
       </c>
       <c r="I14" t="n">
-        <v>114901.53094068952</v>
+        <v>114854.81296311684</v>
       </c>
       <c r="J14" t="n">
         <v>12120.644471936608</v>
@@ -1000,10 +1000,10 @@
         <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>1153.553654175463</v>
+        <v>1153.106391098627</v>
       </c>
       <c r="E15" t="n">
-        <v>42.544109475504676</v>
+        <v>42.52761400584327</v>
       </c>
       <c r="F15" t="n">
         <v>4.491092807202857</v>
@@ -1012,10 +1012,10 @@
         <v>4.49</v>
       </c>
       <c r="H15" t="n">
-        <v>8.472997175046581</v>
+        <v>8.469324245011611</v>
       </c>
       <c r="I15" t="n">
-        <v>115355.36541754629</v>
+        <v>115310.63910986269</v>
       </c>
       <c r="J15" t="n">
         <v>12177.282784524747</v>

--- a/results/mindlin_uniaxial_ssss_table_9_1.xlsx
+++ b/results/mindlin_uniaxial_ssss_table_9_1.xlsx
@@ -36,7 +36,7 @@
     <t>mesh</t>
   </si>
   <si>
-    <t>lambda_cr</t>
+    <t>xi_cr</t>
   </si>
   <si>
     <t>k_num</t>

--- a/results/mindlin_uniaxial_ssss_table_9_1.xlsx
+++ b/results/mindlin_uniaxial_ssss_table_9_1.xlsx
@@ -506,10 +506,10 @@
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>9449.325251489056</v>
+        <v>0.03198253707126428</v>
       </c>
       <c r="E2" t="n">
-        <v>348.49972215323794</v>
+        <v>0.0011795450983481412</v>
       </c>
       <c r="F2" t="n">
         <v>27.040000000000003</v>
@@ -518,10 +518,10 @@
         <v>27.0</v>
       </c>
       <c r="H2" t="n">
-        <v>11.888303334069448</v>
+        <v>0.9999563777700314</v>
       </c>
       <c r="I2" t="n">
-        <v>944932.5251489056</v>
+        <v>3.198253707126428</v>
       </c>
       <c r="J2" t="n">
         <v>73317.06126523524</v>
@@ -530,7 +530,7 @@
         <v>73200.0</v>
       </c>
       <c r="L2" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -544,10 +544,10 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>2505.2745604849683</v>
+        <v>0.07299496425425428</v>
       </c>
       <c r="E3" t="n">
-        <v>92.39680770952431</v>
+        <v>0.002692120768854309</v>
       </c>
       <c r="F3" t="n">
         <v>13.20111111111111</v>
@@ -556,10 +556,10 @@
         <v>13.2</v>
       </c>
       <c r="H3" t="n">
-        <v>5.999169004172367</v>
+        <v>0.9997960686228459</v>
       </c>
       <c r="I3" t="n">
-        <v>250527.45604849682</v>
+        <v>7.299496425425428</v>
       </c>
       <c r="J3" t="n">
         <v>35793.885802607656</v>
@@ -568,7 +568,7 @@
         <v>35800.0</v>
       </c>
       <c r="L3" t="n">
-        <v>65</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -582,10 +582,10 @@
         <v>14</v>
       </c>
       <c r="D4" t="n">
-        <v>1869.036965154195</v>
+        <v>0.10855519444471623</v>
       </c>
       <c r="E4" t="n">
-        <v>68.93178567937693</v>
+        <v>0.0040036144481652505</v>
       </c>
       <c r="F4" t="n">
         <v>8.41</v>
@@ -594,10 +594,10 @@
         <v>8.41</v>
       </c>
       <c r="H4" t="n">
-        <v>7.196407334051954</v>
+        <v>0.9995239459633571</v>
       </c>
       <c r="I4" t="n">
-        <v>186903.6965154195</v>
+        <v>10.855519444471623</v>
       </c>
       <c r="J4" t="n">
         <v>22803.124454165252</v>
@@ -606,7 +606,7 @@
         <v>22800.0</v>
       </c>
       <c r="L4" t="n">
-        <v>78</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -620,10 +620,10 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>1563.3435058769646</v>
+        <v>0.0012450581530993648</v>
       </c>
       <c r="E5" t="n">
-        <v>57.65753246162585</v>
+        <v>4.591887874230771e-5</v>
       </c>
       <c r="F5" t="n">
         <v>6.25</v>
@@ -632,10 +632,10 @@
         <v>6.25</v>
       </c>
       <c r="H5" t="n">
-        <v>8.225205193860136</v>
+        <v>0.9999926529794013</v>
       </c>
       <c r="I5" t="n">
-        <v>156334.35058769645</v>
+        <v>0.12450581530993649</v>
       </c>
       <c r="J5" t="n">
         <v>16946.43612824409</v>
@@ -644,7 +644,7 @@
         <v>16900.0</v>
       </c>
       <c r="L5" t="n">
-        <v>91</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -658,10 +658,10 @@
         <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>1432.9379589723042</v>
+        <v>0.01074173904188596</v>
       </c>
       <c r="E6" t="n">
-        <v>52.848057112435846</v>
+        <v>0.00039616511993276275</v>
       </c>
       <c r="F6" t="n">
         <v>5.137777777777777</v>
@@ -670,10 +670,10 @@
         <v>5.14</v>
       </c>
       <c r="H6" t="n">
-        <v>9.286170285724971</v>
+        <v>0.9999228917370372</v>
       </c>
       <c r="I6" t="n">
-        <v>143293.79589723042</v>
+        <v>1.074173904188596</v>
       </c>
       <c r="J6" t="n">
         <v>13930.723672355674</v>
@@ -682,7 +682,7 @@
         <v>13900.0</v>
       </c>
       <c r="L6" t="n">
-        <v>104</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -696,10 +696,10 @@
         <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>1344.6012112638493</v>
+        <v>0.005811985885963781</v>
       </c>
       <c r="E7" t="n">
-        <v>49.59011739579143</v>
+        <v>0.00021435133329734173</v>
       </c>
       <c r="F7" t="n">
         <v>4.530816326530612</v>
@@ -708,10 +708,10 @@
         <v>4.53</v>
       </c>
       <c r="H7" t="n">
-        <v>9.94507343089852</v>
+        <v>0.9999526903502924</v>
       </c>
       <c r="I7" t="n">
-        <v>134460.12112638494</v>
+        <v>0.5811985885963781</v>
       </c>
       <c r="J7" t="n">
         <v>12284.990317817048</v>
@@ -720,7 +720,7 @@
         <v>12300.0</v>
       </c>
       <c r="L7" t="n">
-        <v>117</v>
+        <v>425</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -734,10 +734,10 @@
         <v>18</v>
       </c>
       <c r="D8" t="n">
-        <v>1168.9713573179058</v>
+        <v>0.011916692501724726</v>
       </c>
       <c r="E8" t="n">
-        <v>43.11272841054829</v>
+        <v>0.00043949847373305335</v>
       </c>
       <c r="F8" t="n">
         <v>4.2025</v>
@@ -746,10 +746,10 @@
         <v>4.2</v>
       </c>
       <c r="H8" t="n">
-        <v>9.258828890076929</v>
+        <v>0.999895419756399</v>
       </c>
       <c r="I8" t="n">
-        <v>116897.13573179058</v>
+        <v>1.1916692501724726</v>
       </c>
       <c r="J8" t="n">
         <v>11394.783652631326</v>
@@ -758,7 +758,7 @@
         <v>11400.0</v>
       </c>
       <c r="L8" t="n">
-        <v>143</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -772,10 +772,10 @@
         <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>1180.272241557562</v>
+        <v>0.02236117637338835</v>
       </c>
       <c r="E9" t="n">
-        <v>43.52951531466988</v>
+        <v>0.0008247005522343899</v>
       </c>
       <c r="F9" t="n">
         <v>4.044567901234568</v>
@@ -784,10 +784,10 @@
         <v>4.04</v>
       </c>
       <c r="H9" t="n">
-        <v>9.762463723598977</v>
+        <v>0.9997960967469521</v>
       </c>
       <c r="I9" t="n">
-        <v>118027.2241557562</v>
+        <v>2.236117637338835</v>
       </c>
       <c r="J9" t="n">
         <v>10966.561856738857</v>
@@ -796,7 +796,7 @@
         <v>11000.0</v>
       </c>
       <c r="L9" t="n">
-        <v>156</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -810,10 +810,10 @@
         <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>1183.5090574494257</v>
+        <v>0.004370437688171491</v>
       </c>
       <c r="E10" t="n">
-        <v>43.64889203300201</v>
+        <v>0.00016118572273462483</v>
       </c>
       <c r="F10" t="n">
         <v>4.0</v>
@@ -822,10 +822,10 @@
         <v>4.0</v>
       </c>
       <c r="H10" t="n">
-        <v>9.912223008250502</v>
+        <v>0.9999597035693163</v>
       </c>
       <c r="I10" t="n">
-        <v>118350.90574494256</v>
+        <v>0.43704376881714907</v>
       </c>
       <c r="J10" t="n">
         <v>10845.71912207622</v>
@@ -834,7 +834,7 @@
         <v>10800.0</v>
       </c>
       <c r="L10" t="n">
-        <v>169</v>
+        <v>625</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -848,10 +848,10 @@
         <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>1208.0682281265051</v>
+        <v>0.0023457836217057114</v>
       </c>
       <c r="E11" t="n">
-        <v>44.55465661719043</v>
+        <v>8.651463661569185e-5</v>
       </c>
       <c r="F11" t="n">
         <v>4.036446280991736</v>
@@ -860,10 +860,10 @@
         <v>4.04</v>
       </c>
       <c r="H11" t="n">
-        <v>10.038089823468072</v>
+        <v>0.99997856663248</v>
       </c>
       <c r="I11" t="n">
-        <v>120806.82281265051</v>
+        <v>0.23457836217057113</v>
       </c>
       <c r="J11" t="n">
         <v>10944.540653746379</v>
@@ -872,7 +872,7 @@
         <v>11000.0</v>
       </c>
       <c r="L11" t="n">
-        <v>182</v>
+        <v>675</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -886,10 +886,10 @@
         <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>1222.3959550351979</v>
+        <v>0.00934220124240165</v>
       </c>
       <c r="E12" t="n">
-        <v>45.083076235933056</v>
+        <v>0.0003445488911246395</v>
       </c>
       <c r="F12" t="n">
         <v>4.134444444444444</v>
@@ -898,10 +898,10 @@
         <v>4.13</v>
       </c>
       <c r="H12" t="n">
-        <v>9.904264609604878</v>
+        <v>0.9999166637995129</v>
       </c>
       <c r="I12" t="n">
-        <v>122239.59550351978</v>
+        <v>0.934220124240165</v>
       </c>
       <c r="J12" t="n">
         <v>11210.255792568223</v>
@@ -910,7 +910,7 @@
         <v>11200.0</v>
       </c>
       <c r="L12" t="n">
-        <v>195</v>
+        <v>725</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -924,10 +924,10 @@
         <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>1169.9353929198705</v>
+        <v>0.00030070024183951667</v>
       </c>
       <c r="E13" t="n">
-        <v>43.14828292163654</v>
+        <v>1.1090098810597004e-5</v>
       </c>
       <c r="F13" t="n">
         <v>4.28171597633136</v>
@@ -936,10 +936,10 @@
         <v>4.28</v>
       </c>
       <c r="H13" t="n">
-        <v>9.077334218372572</v>
+        <v>0.9999974098938669</v>
       </c>
       <c r="I13" t="n">
-        <v>116993.53929198705</v>
+        <v>0.030070024183951667</v>
       </c>
       <c r="J13" t="n">
         <v>11609.572209949069</v>
@@ -948,7 +948,7 @@
         <v>11600.0</v>
       </c>
       <c r="L13" t="n">
-        <v>221</v>
+        <v>825</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -962,10 +962,10 @@
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>1148.5481296311684</v>
+        <v>0.0012523366655901962</v>
       </c>
       <c r="E14" t="n">
-        <v>42.359501171050034</v>
+        <v>4.618731691257218e-5</v>
       </c>
       <c r="F14" t="n">
         <v>4.470204081632653</v>
@@ -974,10 +974,10 @@
         <v>4.47</v>
       </c>
       <c r="H14" t="n">
-        <v>8.475965839031463</v>
+        <v>0.9999896677386381</v>
       </c>
       <c r="I14" t="n">
-        <v>114854.81296311684</v>
+        <v>0.1252336665590196</v>
       </c>
       <c r="J14" t="n">
         <v>12120.644471936608</v>
@@ -986,7 +986,7 @@
         <v>12100.0</v>
       </c>
       <c r="L14" t="n">
-        <v>234</v>
+        <v>875</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1000,10 +1000,10 @@
         <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>1153.106391098627</v>
+        <v>0.010742334898082148</v>
       </c>
       <c r="E15" t="n">
-        <v>42.52761400584327</v>
+        <v>0.00039618709565201126</v>
       </c>
       <c r="F15" t="n">
         <v>4.491092807202857</v>
@@ -1012,10 +1012,10 @@
         <v>4.49</v>
       </c>
       <c r="H15" t="n">
-        <v>8.469324245011611</v>
+        <v>0.9999117838101638</v>
       </c>
       <c r="I15" t="n">
-        <v>115310.63910986269</v>
+        <v>1.0742334898082146</v>
       </c>
       <c r="J15" t="n">
         <v>12177.282784524747</v>
@@ -1024,7 +1024,7 @@
         <v>12200.0</v>
       </c>
       <c r="L15" t="n">
-        <v>234</v>
+        <v>875</v>
       </c>
     </row>
   </sheetData>

--- a/results/mindlin_uniaxial_ssss_table_9_1.xlsx
+++ b/results/mindlin_uniaxial_ssss_table_9_1.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>a/b</t>
   </si>
@@ -37,6 +37,12 @@
   </si>
   <si>
     <t>xi_cr</t>
+  </si>
+  <si>
+    <t>w_participation</t>
+  </si>
+  <si>
+    <t>filtered_modes</t>
   </si>
   <si>
     <t>k_num</t>
@@ -454,10 +460,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -494,8 +500,14 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="n">
         <v>0.2</v>
       </c>
@@ -503,37 +515,43 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03198253707126428</v>
+        <v>3.73016817582937e30</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0011795450983481412</v>
+        <v>0.00205894229689175</v>
       </c>
       <c r="F2" t="n">
+        <v>111</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.3757199993264423e29</v>
+      </c>
+      <c r="H2" t="n">
         <v>27.040000000000003</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>27.0</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.9999563777700314</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.198253707126428</v>
-      </c>
       <c r="J2" t="n">
+        <v>5.087721891000156e27</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.73016817582937e32</v>
+      </c>
+      <c r="L2" t="n">
         <v>73317.06126523524</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>73200.0</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>125</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:14">
       <c r="A3" t="n">
         <v>0.3</v>
       </c>
@@ -541,37 +559,43 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07299496425425428</v>
+        <v>4.5858871524343434e26</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002692120768854309</v>
+        <v>0.005041066388254843</v>
       </c>
       <c r="F3" t="n">
+        <v>199</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.6913169521788084e25</v>
+      </c>
+      <c r="H3" t="n">
         <v>13.20111111111111</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>13.2</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.9997960686228459</v>
-      </c>
-      <c r="I3" t="n">
-        <v>7.299496425425428</v>
-      </c>
       <c r="J3" t="n">
+        <v>1.2811928768293305e24</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.585887152434343e28</v>
+      </c>
+      <c r="L3" t="n">
         <v>35793.885802607656</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>35800.0</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:14">
       <c r="A4" t="n">
         <v>0.4</v>
       </c>
@@ -579,37 +603,43 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>0.10855519444471623</v>
+        <v>4.748452198289087e25</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0040036144481652505</v>
+        <v>0.0005007247409519801</v>
       </c>
       <c r="F4" t="n">
+        <v>240</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.7512724218069482e24</v>
+      </c>
+      <c r="H4" t="n">
         <v>8.41</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>8.41</v>
       </c>
-      <c r="H4" t="n">
-        <v>0.9995239459633571</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10.855519444471623</v>
-      </c>
       <c r="J4" t="n">
+        <v>2.0823691103530895e23</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.7484521982890873e27</v>
+      </c>
+      <c r="L4" t="n">
         <v>22803.124454165252</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>22800.0</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:14">
       <c r="A5" t="n">
         <v>0.5</v>
       </c>
@@ -617,37 +647,43 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0012450581530993648</v>
+        <v>4.706206345774951e22</v>
       </c>
       <c r="E5" t="n">
-        <v>4.591887874230771e-5</v>
+        <v>8.540054883185968e-11</v>
       </c>
       <c r="F5" t="n">
+        <v>274</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.735691766605157e21</v>
+      </c>
+      <c r="H5" t="n">
         <v>6.25</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>6.25</v>
       </c>
-      <c r="H5" t="n">
-        <v>0.9999926529794013</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.12450581530993649</v>
-      </c>
       <c r="J5" t="n">
+        <v>2.777106826568251e20</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.706206345774951e24</v>
+      </c>
+      <c r="L5" t="n">
         <v>16946.43612824409</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>16900.0</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>325</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:14">
       <c r="A6" t="n">
         <v>0.6</v>
       </c>
@@ -655,37 +691,43 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01074173904188596</v>
+        <v>3.0577781588789904e26</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00039616511993276275</v>
+        <v>0.0001216866700637986</v>
       </c>
       <c r="F6" t="n">
+        <v>328</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.1277364366388397e25</v>
+      </c>
+      <c r="H6" t="n">
         <v>5.137777777777777</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>5.14</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.9999228917370372</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.074173904188596</v>
-      </c>
       <c r="J6" t="n">
+        <v>2.19498873913269e24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.0577781588789902e28</v>
+      </c>
+      <c r="L6" t="n">
         <v>13930.723672355674</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>13900.0</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>375</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:14">
       <c r="A7" t="n">
         <v>0.7</v>
       </c>
@@ -693,37 +735,43 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
-        <v>0.005811985885963781</v>
+        <v>2.60535032584392e26</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00021435133329734173</v>
+        <v>8.79560402703598e-5</v>
       </c>
       <c r="F7" t="n">
+        <v>370</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.608769308955411e24</v>
+      </c>
+      <c r="H7" t="n">
         <v>4.530816326530612</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>4.53</v>
       </c>
-      <c r="H7" t="n">
-        <v>0.9999526903502924</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.5811985885963781</v>
-      </c>
       <c r="J7" t="n">
+        <v>2.120758957429013e24</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.60535032584392e28</v>
+      </c>
+      <c r="L7" t="n">
         <v>12284.990317817048</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>12300.0</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:14">
       <c r="A8" t="n">
         <v>0.8</v>
       </c>
@@ -731,37 +779,43 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>0.011916692501724726</v>
+        <v>6.544102996924546e26</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00043949847373305335</v>
+        <v>0.026568723717964548</v>
       </c>
       <c r="F8" t="n">
+        <v>453</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.413524791953784e25</v>
+      </c>
+      <c r="H8" t="n">
         <v>4.2025</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>4.2</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.999895419756399</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.1916692501724726</v>
-      </c>
       <c r="J8" t="n">
+        <v>5.743069106374263e24</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.544102996924546e28</v>
+      </c>
+      <c r="L8" t="n">
         <v>11394.783652631326</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>11400.0</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>525</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:14">
       <c r="A9" t="n">
         <v>0.9</v>
       </c>
@@ -769,37 +823,43 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02236117637338835</v>
+        <v>3.181616846102398e23</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0008247005522343899</v>
+        <v>7.081715320711451e-8</v>
       </c>
       <c r="F9" t="n">
+        <v>491</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.1734092724663273e22</v>
+      </c>
+      <c r="H9" t="n">
         <v>4.044567901234568</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>4.04</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.9997960967469521</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.236117637338835</v>
-      </c>
       <c r="J9" t="n">
+        <v>2.9011981035307994e21</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.1816168461023976e25</v>
+      </c>
+      <c r="L9" t="n">
         <v>10966.561856738857</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>11000.0</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>575</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:14">
       <c r="A10" t="n">
         <v>1.0</v>
       </c>
@@ -807,37 +867,43 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004370437688171491</v>
+        <v>1.651202841237288e29</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00016118572273462483</v>
+        <v>0.013263645929131871</v>
       </c>
       <c r="F10" t="n">
+        <v>530</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.089786477602214e27</v>
+      </c>
+      <c r="H10" t="n">
         <v>4.0</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>4.0</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.9999597035693163</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.43704376881714907</v>
-      </c>
       <c r="J10" t="n">
+        <v>1.5224466194005536e27</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.651202841237288e31</v>
+      </c>
+      <c r="L10" t="n">
         <v>10845.71912207622</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>10800.0</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>625</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:14">
       <c r="A11" t="n">
         <v>1.1</v>
       </c>
@@ -845,37 +911,43 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0023457836217057114</v>
+        <v>3.5993869758634554e24</v>
       </c>
       <c r="E11" t="n">
-        <v>8.651463661569185e-5</v>
+        <v>7.762645738722899e-6</v>
       </c>
       <c r="F11" t="n">
+        <v>557</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.3274867015639316e23</v>
+      </c>
+      <c r="H11" t="n">
         <v>4.036446280991736</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>4.04</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.99997856663248</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.23457836217057113</v>
-      </c>
       <c r="J11" t="n">
+        <v>3.2887510675300607e22</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.5993869758634556e26</v>
+      </c>
+      <c r="L11" t="n">
         <v>10944.540653746379</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>11000.0</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>675</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:14">
       <c r="A12" t="n">
         <v>1.2</v>
       </c>
@@ -883,37 +955,43 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00934220124240165</v>
+        <v>2.5384928302675338e26</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0003445488911246395</v>
+        <v>0.004078932460137892</v>
       </c>
       <c r="F12" t="n">
+        <v>610</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9.36219277558272e24</v>
+      </c>
+      <c r="H12" t="n">
         <v>4.134444444444444</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>4.13</v>
       </c>
-      <c r="H12" t="n">
-        <v>0.9999166637995129</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.934220124240165</v>
-      </c>
       <c r="J12" t="n">
+        <v>2.2644379193830822e24</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.538492830267534e28</v>
+      </c>
+      <c r="L12" t="n">
         <v>11210.255792568223</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>11200.0</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>725</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:14">
       <c r="A13" t="n">
         <v>1.3</v>
       </c>
@@ -921,37 +999,43 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D13" t="n">
-        <v>0.00030070024183951667</v>
+        <v>4.631508227705725e25</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1090098810597004e-5</v>
+        <v>0.00018920802816208015</v>
       </c>
       <c r="F13" t="n">
+        <v>679</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.708142420276547e24</v>
+      </c>
+      <c r="H13" t="n">
         <v>4.28171597633136</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>4.28</v>
       </c>
-      <c r="H13" t="n">
-        <v>0.9999974098938669</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.030070024183951667</v>
-      </c>
       <c r="J13" t="n">
+        <v>3.9893875019241925e23</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.631508227705725e27</v>
+      </c>
+      <c r="L13" t="n">
         <v>11609.572209949069</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>11600.0</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>825</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:14">
       <c r="A14" t="n">
         <v>1.4</v>
       </c>
@@ -959,37 +1043,43 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0012523366655901962</v>
+        <v>2.164047125117828e24</v>
       </c>
       <c r="E14" t="n">
-        <v>4.618731691257218e-5</v>
+        <v>2.1476461157354093e-6</v>
       </c>
       <c r="F14" t="n">
+        <v>715</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.98120290876041e22</v>
+      </c>
+      <c r="H14" t="n">
         <v>4.470204081632653</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>4.47</v>
       </c>
-      <c r="H14" t="n">
-        <v>0.9999896677386381</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.1252336665590196</v>
-      </c>
       <c r="J14" t="n">
+        <v>1.7854224914593683e22</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.1640471251178282e26</v>
+      </c>
+      <c r="L14" t="n">
         <v>12120.644471936608</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>12100.0</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>875</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:14">
       <c r="A15" t="n">
         <v>1.41</v>
       </c>
@@ -997,33 +1087,39 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D15" t="n">
-        <v>0.010742334898082148</v>
+        <v>1.153113174425952e21</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00039618709565201126</v>
+        <v>1.7751672012287293e-12</v>
       </c>
       <c r="F15" t="n">
+        <v>679</v>
+      </c>
+      <c r="G15" t="n">
+        <v>4.252786418113358e19</v>
+      </c>
+      <c r="H15" t="n">
         <v>4.491092807202857</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>4.49</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.9999117838101638</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.0742334898082146</v>
-      </c>
       <c r="J15" t="n">
+        <v>9.469379949781264e18</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.153113174425952e23</v>
+      </c>
+      <c r="L15" t="n">
         <v>12177.282784524747</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>12200.0</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>875</v>
       </c>
     </row>

--- a/results/mindlin_uniaxial_ssss_table_9_1.xlsx
+++ b/results/mindlin_uniaxial_ssss_table_9_1.xlsx
@@ -15,6 +15,7 @@
   <sheets>
     <sheet name="Table 9-1" sheetId="1" r:id="rId1"/>
     <sheet name="Spectrum" sheetId="2" r:id="rId5"/>
+    <sheet name="MatrixBlocks" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr fullCalcOnLoad="1" calcMode="auto"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1499" uniqueCount="57">
   <si>
     <t>a/b</t>
   </si>
@@ -146,6 +147,57 @@
   </si>
   <si>
     <t>first_positive</t>
+  </si>
+  <si>
+    <t>xi_selected</t>
+  </si>
+  <si>
+    <t>norm_kww</t>
+  </si>
+  <si>
+    <t>norm_kqq</t>
+  </si>
+  <si>
+    <t>norm_kqw</t>
+  </si>
+  <si>
+    <t>norm_kgww</t>
+  </si>
+  <si>
+    <t>norm_kgqq</t>
+  </si>
+  <si>
+    <t>ratio_kqq_kww</t>
+  </si>
+  <si>
+    <t>ratio_kqw_geom_mean</t>
+  </si>
+  <si>
+    <t>ratio_kgqq_kgww</t>
+  </si>
+  <si>
+    <t>energy_kww</t>
+  </si>
+  <si>
+    <t>energy_kqq</t>
+  </si>
+  <si>
+    <t>energy_kqw</t>
+  </si>
+  <si>
+    <t>energy_K_total</t>
+  </si>
+  <si>
+    <t>energy_kgww</t>
+  </si>
+  <si>
+    <t>energy_kgqq</t>
+  </si>
+  <si>
+    <t>energy_KG_total</t>
+  </si>
+  <si>
+    <t>rayleigh_xi</t>
   </si>
 </sst>
 </file>
@@ -32242,4 +32294,1124 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98E33B40-677E-409B-9433-118218E4161E}">
+  <dimension ref="A1:X15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:24">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" t="s">
+        <v>48</v>
+      </c>
+      <c r="P1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T1" t="s">
+        <v>53</v>
+      </c>
+      <c r="U1" t="s">
+        <v>54</v>
+      </c>
+      <c r="V1" t="s">
+        <v>55</v>
+      </c>
+      <c r="W1" t="s">
+        <v>56</v>
+      </c>
+      <c r="X1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="n">
+        <v>187</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1917.7035290964736</v>
+      </c>
+      <c r="F2" t="n">
+        <v>733.1706126523525</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.6156306540423095</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7.499794218391554e14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6.412558208788371e6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6.530856253386203e6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>24.587648711217753</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.4037892128328902</v>
+      </c>
+      <c r="M2" t="n">
+        <v>8.550312211317769e-9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>9.417373410449134e-5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.016422441103474336</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-2.005528370202494e-11</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.0841649766168276e-10</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4.0452156792064085e-11</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.288133707517219e-10</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8.911520825938092e-17</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4.90807545109501e-19</v>
+      </c>
+      <c r="V2" t="n">
+        <v>8.960601580449043e-17</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.669545708506371e6</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.4339972956371624e-18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="n">
+        <v>349</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2450.694798549614</v>
+      </c>
+      <c r="F3" t="n">
+        <v>357.93885802607656</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6.8466855263059365</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.590604959149538e14</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.951201125633603e6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9.185179685143996e6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>47.229120774449676</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.1865768729109538</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.1792473951426012e-8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.00011143171226502727</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.025123839983760107</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-2.1676031476340702e-14</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5.860647752952044e-10</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.72219974314596e-14</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5.860803212611596e-10</v>
+      </c>
+      <c r="T3" t="n">
+        <v>9.336135847933039e-20</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6.184409227698423e-22</v>
+      </c>
+      <c r="V3" t="n">
+        <v>9.397979940210023e-20</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6.236237201928546e9</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.4464038191924565e-21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="n">
+        <v>423</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2340.6386674970336</v>
+      </c>
+      <c r="F4" t="n">
+        <v>228.03124454165254</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10.264552439740287</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.924146543567866e14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9.971017696524348e6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.0212279122286238e7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>49.68312009985336</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.1187468456905154</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.2583080892942287e-8</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.00011488853291343685</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02251764469385282</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-3.80242007312859e-17</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-7.490415977547059e-10</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7.611673164566108e-17</v>
+      </c>
+      <c r="S4" t="n">
+        <v>-7.490415596621749e-10</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.6466516995039805e-22</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.0516625814337689e-24</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.657168325318318e-22</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-4.5200089104907e12</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.705223001111302e-24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="n">
+        <v>512</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2260.6629511977007</v>
+      </c>
+      <c r="F5" t="n">
+        <v>169.46436128244093</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13.340049400888041</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.249579093123921e14</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.0941325622510813e7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.1195558938306803e7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>52.373657500845276</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.1032066714868038</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.3262889535334572e-8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.00011784059147034152</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.021064151791747573</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-9.899058984756422e-16</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.35580505217493e-10</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.91259737966803e-15</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.355814279089742e-10</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.307023779189057e-21</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.681968171644446e-23</v>
+      </c>
+      <c r="V5" t="n">
+        <v>4.333843460905501e-21</v>
+      </c>
+      <c r="W5" t="n">
+        <v>5.435854571908153e10</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.147596175941462e-22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="n">
+        <v>585</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2206.004856028181</v>
+      </c>
+      <c r="F6" t="n">
+        <v>139.30723672355674</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15.835536673559957</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.565635881462195e14</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.1853767408515127e7</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.2122683178297367e7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>55.092592592727456</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.109680148817123</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.3838747727029966e-8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.00012030695921307594</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.02014209345747158</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1.3767199114572018e-15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-2.841846586310042e-10</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.7800089990126264e-15</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-2.841832553419166e-10</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6.013581268161439e-21</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.6771009455296755e-23</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.050352277616735e-21</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-4.696970396141262e10</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.3501856075253777e-22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="n">
+        <v>665</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2165.8400680847813</v>
+      </c>
+      <c r="F7" t="n">
+        <v>122.84990317817048</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17.629969678882375</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8.872250030327431e14</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.2712449001294311e7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.2996426257950738e7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>57.768183400274246</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.126872731225214</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.432832591263792e-8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.00012237492791292238</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.019506805734518982</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1.1642056835522048e-13</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-3.835304365160923e-9</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.4875392944714983e-13</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-3.835272031799831e-9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.105935809284758e-19</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.0800371061198064e-21</v>
+      </c>
+      <c r="V7" t="n">
+        <v>5.136736180345956e-19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-7.466359760647719e9</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.606634616088962e-21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="n">
+        <v>809</v>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>24.533047743264348</v>
+      </c>
+      <c r="F8" t="n">
+        <v>113.94783652631327</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.21530068925528992</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.956244780886261e14</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.419659618749183e7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.454442751720732e7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>70.7677733097102</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.5870163407792997</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.5851058713568357e-8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.00012898569250867443</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.02242569274906862</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-5.361241674136914e-15</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-3.4386327058452106e-10</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.0722728600176454e-14</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-3.43857909097595e-10</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.511946210855089e-21</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.5277198387711728e-27</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.5119487385749275e-21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-1.3688890374915517e11</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.6423688633300784e-21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="n">
+        <v>897</v>
+      </c>
+      <c r="D9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" t="n">
+        <v>31.516305650681687</v>
+      </c>
+      <c r="F9" t="n">
+        <v>109.66561856738858</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2873854728801369</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9.24452145847404e14</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.4887416888683323e7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.5243817337688863e7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>72.61941009655716</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.570036637274563</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.6104042762577714e-8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0001299396951914399</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.02162006872800248</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-2.1569040414804704e-13</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-6.917197246877115e-10</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4.31395517176312e-13</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-6.915040195746832e-10</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.0791535734887942e-19</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.225928878465416e-25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.0791567994176726e-19</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-6.407817843966956e9</v>
+      </c>
+      <c r="X9" t="n">
+        <v>5.991126990417819e-20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="n">
+        <v>960</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10.205625737586656</v>
+      </c>
+      <c r="F10" t="n">
+        <v>108.4571912207622</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.09409819323841176</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.525793420141938e14</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.5558677670683092e7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.5924653686795913e7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>74.50950722345817</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.5642403907364097</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.6333209197865707e-8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.00013080762943125818</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.020993836209990832</v>
+      </c>
+      <c r="P10" t="n">
+        <v>-4.176287806422784e-14</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.106629041151253e-10</v>
+      </c>
+      <c r="R10" t="n">
+        <v>8.352652949175429e-14</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.1070466776655282e-10</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.6529125923433587e-20</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8.98760848440952e-27</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.652913491104207e-20</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2747470989893991e10</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.2691054170271408e-20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2243.7106345025427</v>
+      </c>
+      <c r="F11" t="n">
+        <v>109.44540653746378</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20.500729135073456</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.800281144610422e14</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.6209955548037726e7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.6586059005591454e7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>76.41166285454621</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.56595426867247</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.6540296455629997e-8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.00013159307238778337</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.020493655159073684</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1.3065149810872683e-17</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-4.849132778233489e-10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.531562344462246e-17</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-4.849132655728753e-10</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.570725970764781e-23</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.4546341130500185e-25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.605272311895281e-23</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-8.651020656816477e12</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.162416680057787e-24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1124</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.85976471229201</v>
+      </c>
+      <c r="F12" t="n">
+        <v>112.10255792568223</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.15039589661699865</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.0068272836652099e15</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.684172762111953e7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.7228241623691626e7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>78.31000385904942</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.5728786825765502</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.6727524069281915e-8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.00013230313844865273</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.020085284191884125</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-6.247968141225357e-15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-2.7336471706717862e-11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.2495147728935969e-14</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-2.7330224527130152e-11</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.312444010769465e-21</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.0215667940363472e-27</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.312445032336259e-21</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-2.0823900318690014e10</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.8634273208147127e-21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1297</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="n">
+        <v>9.222787789005366</v>
+      </c>
+      <c r="F13" t="n">
+        <v>116.09572209949069</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.07944123712932077</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.0142835963731691e15</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.7991105308307026e7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.8426598025837656e7</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.3725966023685</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.9298695936991923</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.7737746496777463e-8</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.00013640696247271423</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.02183787359312999</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-2.493895803898777e-16</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-2.3163509145202332e-10</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.976189121345734e-16</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-2.3163484322269156e-10</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.953431767712288e-23</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.8612935507655176e-30</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3.9534322538416433e-23</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-5.859082143056999e12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5.0020692373047525e-23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1382</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2274.9425836764576</v>
+      </c>
+      <c r="F14" t="n">
+        <v>121.20644471936609</v>
+      </c>
+      <c r="G14" t="n">
+        <v>18.769155294866696</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.0399113853216549e15</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.854595404819854e7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.8988898778718166e7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>89.8957773611633</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.9210244430601622</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.7834167708878475e-8</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.00013673415882913095</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.021369462498136</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-1.479786155693674e-11</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-3.2673460382640525e-10</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.988969386461604e-11</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-3.1164277151872594e-10</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6.45356159794967e-17</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.036572757503118e-19</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.493927325524701e-17</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-4.798987667967867e6</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.4996894732602593e-19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D15" t="n">
+        <v>7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2256.6670594025527</v>
+      </c>
+      <c r="F15" t="n">
+        <v>121.77282784524746</v>
+      </c>
+      <c r="G15" t="n">
+        <v>18.531778388774814</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.0442295698445788e15</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.854676434482126e7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.8986593682227634e7</v>
+      </c>
+      <c r="K15" t="n">
+        <v>89.25821865647436</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.8860191068087233</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.7761194358422284e-8</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.00013643160428698662</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.02112992097755606</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-3.294241527395059e-14</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.3262510974848136e-9</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6.653458788701609e-14</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.3262846896574266e-9</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.4347735328064761e-19</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8.927423985109288e-22</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.4437009567915854e-19</v>
+      </c>
+      <c r="W15" t="n">
+        <v>9.186699526783585e9</v>
+      </c>
+      <c r="X15" t="n">
+        <v>6.3007645087956515e-22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>